--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92455</v>
+        <v>92458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93320</v>
+        <v>93323</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93323</v>
+        <v>93324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
